--- a/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-EX-Beneficiary.xlsx
+++ b/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-EX-Beneficiary.xlsx
@@ -1324,7 +1324,7 @@
         <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>108</v>
